--- a/в бланки заводов/Останкино КИ/ostankino_ki/UZ/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/UZ/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\UZ\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1731C220-8734-4216-8A83-5B87F7CE1FB0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C79471A-C187-4467-A558-B50517951B0D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$62</definedName>
   </definedNames>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="93">
   <si>
     <t>1С</t>
   </si>
@@ -292,6 +292,27 @@
   </si>
   <si>
     <t>МОЛОЧНЫЕ КЛАССИЧЕСКИЕ сос п/о в/у 0.3кг</t>
+  </si>
+  <si>
+    <t>5179 АРОМАТНАЯ с/к с/н в/у 1/100_СНГ  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>5681 САЛЯМИ ИТАЛЬЯНСКАЯ с/к в/у 1/150_СНГ_60с  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>6616 МОЛОЧНЫЕ КЛАССИЧЕСКИЕ сос п/о в/у 0.3кг  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>6773 САЛЯМИ Папа может п/к в/у 0.28кг 8шт.</t>
+  </si>
+  <si>
+    <t>7231 КЛАССИЧЕСКАЯ ПМ вар п/о 0.3кг 8шт_209к  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7230 СЕРВЕЛАТ КАРЕЛЬС.вк в/у 0.28кг_СНГ_209к  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7332 БОЯРСКАЯ ПМ п/к в/у 0.28кг_СНГ  ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -734,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -1412,28 +1433,105 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="8">
+        <v>1001304507230</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B60" s="8">
         <v>1001191975179</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C60" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="10" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" s="8">
+        <v>1001191975179</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B62" s="11">
         <v>1001024976616</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C62" s="15" t="s">
         <v>85</v>
       </c>
     </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1001190765681</v>
+      </c>
+      <c r="C63" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1001024976616</v>
+      </c>
+      <c r="C64" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1001303107241</v>
+      </c>
+      <c r="C65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1001013957231</v>
+      </c>
+      <c r="C66" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1001301777332</v>
+      </c>
+      <c r="C67" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C60" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C62" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/UZ/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/UZ/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\UZ\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C79471A-C187-4467-A558-B50517951B0D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6023CC9-2A7B-426D-BA2B-15D6248C454D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$69</definedName>
   </definedNames>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="95">
   <si>
     <t>1С</t>
   </si>
@@ -313,6 +313,12 @@
   </si>
   <si>
     <t>7332 БОЯРСКАЯ ПМ п/к в/у 0.28кг_СНГ  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>6207 ОКОРОК КОПЧЕНЫЙ к/в мл/к в/у 0.3кг_СНГ  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>6549 МЯСНЫЕ Папа может сар б/о мгс 1*3_Х5_45с  ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -755,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -1367,7 +1373,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B53" s="8">
         <v>1001032736549</v>
@@ -1378,160 +1384,182 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B54" s="8">
-        <v>1001083446207</v>
+        <v>1001032736549</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B55" s="8">
-        <v>1001031076548</v>
+        <v>1001083446207</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B56" s="8">
-        <v>1001190765681</v>
+        <v>1001083446207</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B57" s="8">
-        <v>1001013957231</v>
+        <v>1001031076548</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B58" s="8">
-        <v>1001304507230</v>
+        <v>1001190765681</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B59" s="8">
-        <v>1001304507230</v>
+        <v>1001013957231</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B60" s="8">
-        <v>1001191975179</v>
+        <v>1001304507230</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" s="8">
+        <v>1001304507230</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" s="8">
+        <v>1001191975179</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B63" s="8">
         <v>1001191975179</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C63" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="10" t="s">
+    <row r="64" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B64" s="11">
         <v>1001024976616</v>
       </c>
-      <c r="C62" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B63" s="3">
-        <v>1001190765681</v>
-      </c>
-      <c r="C63" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B64" s="3">
-        <v>1001024976616</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="C64" s="15" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B65" s="3">
-        <v>1001303107241</v>
+        <v>1001190765681</v>
       </c>
       <c r="C65" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B66" s="3">
-        <v>1001013957231</v>
+        <v>1001024976616</v>
       </c>
       <c r="C66" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1001303107241</v>
+      </c>
+      <c r="C67" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1001013957231</v>
+      </c>
+      <c r="C68" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B69" s="3">
         <v>1001301777332</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C69" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C62" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C69" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
